--- a/output/pdf_financials_xlsx/WCM.A.xlsx
+++ b/output/pdf_financials_xlsx/WCM.A.xlsx
@@ -1114,15 +1114,11 @@
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.022</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2572,37 +2568,37 @@
         <v>4.139</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>5.82</v>
+        <v>0.002174</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003993</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00359</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001642</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003077</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005074</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.001924</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.004007</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.010664</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.036307</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.02401</v>
       </c>
     </row>
     <row r="35">
@@ -2688,37 +2684,37 @@
         <v>4.139</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>5.82</v>
+        <v>0.002174</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003993</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00359</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.001642</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003077</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005074</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.001924</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.004007</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.010664</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.036307</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.02401</v>
       </c>
     </row>
     <row r="37">
@@ -3387,16 +3383,16 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00505</v>
+        <v>0.001057</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.004704</v>
+        <v>0.001114</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.003268</v>
+        <v>0.001626</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.003241</v>
+        <v>0.000164</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -9401,7 +9397,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -19638,7 +19634,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -65820,7 +65816,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">

--- a/output/pdf_financials_xlsx/WCM.A.xlsx
+++ b/output/pdf_financials_xlsx/WCM.A.xlsx
@@ -1375,10 +1375,10 @@
         <v>-0.002621</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.001818</v>
+        <v>-0.001884</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.001952</v>
+        <v>-0.001677</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-8.3e-05</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.000479</v>
+        <v>0.000479</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.000192</v>
+        <v>-0.000192</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0.016</v>
@@ -1437,16 +1437,16 @@
         <v>-0.000135</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-3.3e-05</v>
+        <v>3.3e-05</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.000275</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.00151</v>
+        <v>-0.00151</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.005683</v>
+        <v>0.001872</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>9.6e-05</v>
@@ -2155,10 +2155,10 @@
         <v>-0.002621</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.001818</v>
+        <v>-0.001884</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.001952</v>
+        <v>-0.001677</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-8.3e-05</v>
@@ -2279,10 +2279,10 @@
         <v>-0.001705</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.001818</v>
+        <v>-0.001884</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.001952</v>
+        <v>-0.001677</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-8.3e-05</v>
@@ -2349,10 +2349,10 @@
         <v>-61.0236220472441</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-683.4586466165414</v>
+        <v>-708.2706766917294</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1952</v>
+        <v>-1677</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2425,16 +2425,16 @@
         <v>-5.150705837466616</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-1.815181518151815</v>
+        <v>-1.751592356687898</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-16.39833035181872</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-1819.277108433735</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.26885608114894</v>
+        <v>4.700210906899668</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-26.3013698630137</v>
@@ -4752,19 +4752,19 @@
         <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
     </row>
     <row r="71">
@@ -4810,19 +4810,19 @@
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
     </row>
     <row r="72">
@@ -5042,19 +5042,19 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.000686</v>
+        <v>0.0006669999999999999</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.000946</v>
+        <v>0.000908</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.001009</v>
+        <v>0.000971</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.002401</v>
+        <v>0.002363</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.000775</v>
+        <v>0.000737</v>
       </c>
     </row>
     <row r="76">
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.002315702056982241</v>
+        <v>0.002619138878241983</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.001696030411579794</v>
+        <v>0.002251626580890416</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.001192095704248068</v>
+        <v>0.001725032607323675</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.001435155797201446</v>
+        <v>0.002483923495156349</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.0005055895736194596</v>
+        <v>0.00157294534014943</v>
       </c>
     </row>
     <row r="81">
@@ -9894,7 +9894,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -11349,7 +11353,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -14440,7 +14448,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -31738,7 +31750,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -32225,7 +32241,11 @@
           <t>Deferred income tax expense (recovery) 10</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -35575,7 +35595,11 @@
           <t>Deferred income tax expense 14</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -37377,7 +37401,11 @@
           <t>Deferred income tax expense 12</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -38684,7 +38712,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -39492,7 +39524,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -42084,7 +42120,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -49258,7 +49298,11 @@
           <t>Current income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -49357,7 +49401,11 @@
           <t>Deferred income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -51828,7 +51876,11 @@
           <t>Deferred income tax recovery (expense) 14</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -57333,7 +57385,11 @@
           <t>Deferred income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -59432,7 +59488,11 @@
           <t>Income tax recovery 7</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
           <t>-</t>
@@ -60806,7 +60866,11 @@
           <t>Income tax recovery (expense) 8</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
           <t>-</t>
@@ -60905,7 +60969,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -70210,7 +70278,11 @@
           <t>Income tax recovery 9</t>
         </is>
       </c>
-      <c r="D617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E617" t="inlineStr">
         <is>
           <t>-</t>
@@ -71010,7 +71082,11 @@
           <t>Income tax recovery (expense) 8</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E625" s="5" t="n">
         <v>-0.000479</v>
       </c>
